--- a/Nuevos DeepWins/Problem4_Bullseye5/Res/Comparativa_9_Neuronas.xlsx
+++ b/Nuevos DeepWins/Problem4_Bullseye5/Res/Comparativa_9_Neuronas.xlsx
@@ -581,7 +581,7 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.187279</v>
+        <v>0.190524</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -598,25 +598,25 @@
         <v>200000</v>
       </c>
       <c r="G2" t="n">
-        <v>0.584615</v>
+        <v>0.558735</v>
       </c>
       <c r="H2" t="n">
-        <v>0.53605</v>
+        <v>0.581505</v>
       </c>
       <c r="I2" t="n">
-        <v>0.55928</v>
+        <v>0.569892</v>
       </c>
       <c r="J2" t="n">
-        <v>0.187293</v>
+        <v>0.189771</v>
       </c>
       <c r="K2" t="n">
-        <v>0.581081</v>
+        <v>0.597015</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5058820000000001</v>
+        <v>0.470588</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5408809999999999</v>
+        <v>0.526316</v>
       </c>
       <c r="N2" t="n">
         <v>0.2</v>
@@ -652,7 +652,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_14.txt</t>
+          <t>_2_9_1_1790731855_0.txt</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -682,7 +682,7 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.179942</v>
+        <v>0.184782</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -699,25 +699,25 @@
         <v>200000</v>
       </c>
       <c r="G3" t="n">
-        <v>0.622614</v>
+        <v>0.597633</v>
       </c>
       <c r="H3" t="n">
-        <v>0.664577</v>
+        <v>0.633229</v>
       </c>
       <c r="I3" t="n">
-        <v>0.642911</v>
+        <v>0.614916</v>
       </c>
       <c r="J3" t="n">
-        <v>0.181995</v>
+        <v>0.1858</v>
       </c>
       <c r="K3" t="n">
-        <v>0.630682</v>
+        <v>0.605882</v>
       </c>
       <c r="L3" t="n">
-        <v>0.652941</v>
+        <v>0.605882</v>
       </c>
       <c r="M3" t="n">
-        <v>0.641618</v>
+        <v>0.605882</v>
       </c>
       <c r="N3" t="n">
         <v>0.2</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_18.txt</t>
+          <t>_2_9_1_1790731855_12.txt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -783,7 +783,7 @@
         <v>0.1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.186458</v>
+        <v>0.175709</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -800,25 +800,25 @@
         <v>200000</v>
       </c>
       <c r="G4" t="n">
-        <v>0.586207</v>
+        <v>0.60089</v>
       </c>
       <c r="H4" t="n">
-        <v>0.559561</v>
+        <v>0.634796</v>
       </c>
       <c r="I4" t="n">
-        <v>0.572574</v>
+        <v>0.617378</v>
       </c>
       <c r="J4" t="n">
-        <v>0.183805</v>
+        <v>0.175519</v>
       </c>
       <c r="K4" t="n">
-        <v>0.594771</v>
+        <v>0.602339</v>
       </c>
       <c r="L4" t="n">
-        <v>0.535294</v>
+        <v>0.605882</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5634670000000001</v>
+        <v>0.604106</v>
       </c>
       <c r="N4" t="n">
         <v>0.2</v>
@@ -854,7 +854,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_16.txt</t>
+          <t>_2_9_1_1790731855_5.txt</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -884,43 +884,35 @@
         <v>0.1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.187204</v>
+        <v>0.239731</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1790731855</v>
+        <v>1790731906</v>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="F5" t="n">
         <v>200000</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.605422</v>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.630094</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.6175119999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>0.185579</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.6172840000000001</v>
-      </c>
+        <v>0.244998</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0.588235</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.60241</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
         <v>0.2</v>
       </c>
@@ -955,23 +947,23 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_7.txt</t>
+          <t>_2_3_3_3_1_1790731906_2.txt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z5" t="n">
         <v>9</v>
       </c>
       <c r="AA5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -985,7 +977,7 @@
         <v>0.1</v>
       </c>
       <c r="B6" t="n">
-        <v>0.232982</v>
+        <v>0.236621</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1007,7 +999,7 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>0.239653</v>
+        <v>0.242262</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
@@ -1048,7 +1040,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_1.txt</t>
+          <t>_2_3_3_3_1_1790731906_3.txt</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1078,43 +1070,35 @@
         <v>0.1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.178531</v>
+        <v>0.232498</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1790731855</v>
+        <v>1790731906</v>
       </c>
       <c r="E7" t="n">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="F7" t="n">
         <v>200000</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.62543</v>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.570533</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.5967209999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>0.177521</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.639456</v>
-      </c>
+        <v>0.241625</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>0.552941</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.59306</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
         <v>0.2</v>
       </c>
@@ -1149,23 +1133,23 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_8.txt</t>
+          <t>_2_3_3_3_1_1790731906_14.txt</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z7" t="n">
         <v>9</v>
       </c>
       <c r="AA7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1179,7 +1163,7 @@
         <v>0.1</v>
       </c>
       <c r="B8" t="n">
-        <v>0.190524</v>
+        <v>0.18741</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1196,25 +1180,25 @@
         <v>200000</v>
       </c>
       <c r="G8" t="n">
-        <v>0.558735</v>
+        <v>0.565035</v>
       </c>
       <c r="H8" t="n">
-        <v>0.581505</v>
+        <v>0.633229</v>
       </c>
       <c r="I8" t="n">
-        <v>0.569892</v>
+        <v>0.597191</v>
       </c>
       <c r="J8" t="n">
-        <v>0.189771</v>
+        <v>0.185941</v>
       </c>
       <c r="K8" t="n">
-        <v>0.597015</v>
+        <v>0.577778</v>
       </c>
       <c r="L8" t="n">
-        <v>0.470588</v>
+        <v>0.611765</v>
       </c>
       <c r="M8" t="n">
-        <v>0.526316</v>
+        <v>0.594286</v>
       </c>
       <c r="N8" t="n">
         <v>0.2</v>
@@ -1250,7 +1234,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_0.txt</t>
+          <t>_2_9_1_1790731855_17.txt</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1280,43 +1264,35 @@
         <v>0.1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.195504</v>
+        <v>0.233962</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1790731855</v>
+        <v>1790731906</v>
       </c>
       <c r="E9" t="n">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="F9" t="n">
         <v>200000</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.547198</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.581505</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.5638300000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>0.193585</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.606557</v>
-      </c>
+        <v>0.240591</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>0.652941</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.628895</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
         <v>0.2</v>
       </c>
@@ -1351,23 +1327,23 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_19.txt</t>
+          <t>_2_3_3_3_1_1790731906_6.txt</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z9" t="n">
         <v>9</v>
       </c>
       <c r="AA9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1381,35 +1357,43 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>0.235884</v>
+        <v>0.184698</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1790731906</v>
+        <v>1790731855</v>
       </c>
       <c r="E10" t="n">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="F10" t="n">
         <v>200000</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>0.587912</v>
+      </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>0.6708460000000001</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.626647</v>
+      </c>
       <c r="J10" t="n">
-        <v>0.240593</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+        <v>0.182747</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.594444</v>
+      </c>
       <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
+        <v>0.629412</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.611429</v>
+      </c>
       <c r="N10" t="n">
         <v>0.2</v>
       </c>
@@ -1444,23 +1428,23 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_9.txt</t>
+          <t>_2_9_1_1790731855_4.txt</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z10" t="n">
         <v>9</v>
       </c>
       <c r="AA10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1474,7 +1458,7 @@
         <v>0.1</v>
       </c>
       <c r="B11" t="n">
-        <v>0.184782</v>
+        <v>0.179406</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1491,25 +1475,25 @@
         <v>200000</v>
       </c>
       <c r="G11" t="n">
-        <v>0.597633</v>
+        <v>0.576816</v>
       </c>
       <c r="H11" t="n">
-        <v>0.633229</v>
+        <v>0.647335</v>
       </c>
       <c r="I11" t="n">
-        <v>0.614916</v>
+        <v>0.610044</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1858</v>
+        <v>0.177572</v>
       </c>
       <c r="K11" t="n">
-        <v>0.605882</v>
+        <v>0.576923</v>
       </c>
       <c r="L11" t="n">
-        <v>0.605882</v>
+        <v>0.6176469999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.605882</v>
+        <v>0.596591</v>
       </c>
       <c r="N11" t="n">
         <v>0.2</v>
@@ -1545,7 +1529,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_12.txt</t>
+          <t>_2_9_1_1790731855_9.txt</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1575,35 +1559,43 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.236222</v>
+        <v>0.180299</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1790731906</v>
+        <v>1790731855</v>
       </c>
       <c r="E12" t="n">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="F12" t="n">
         <v>200000</v>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>0.611501</v>
+      </c>
       <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>0.683386</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.645448</v>
+      </c>
       <c r="J12" t="n">
-        <v>0.242453</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
+        <v>0.178741</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.623711</v>
+      </c>
       <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
+        <v>0.711765</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.664835</v>
+      </c>
       <c r="N12" t="n">
         <v>0.2</v>
       </c>
@@ -1638,23 +1630,23 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_13.txt</t>
+          <t>_2_9_1_1790731855_13.txt</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z12" t="n">
         <v>9</v>
       </c>
       <c r="AA12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1668,7 +1660,7 @@
         <v>0.1</v>
       </c>
       <c r="B13" t="n">
-        <v>0.236621</v>
+        <v>0.200892</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1684,19 +1676,27 @@
       <c r="F13" t="n">
         <v>200000</v>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>0.480272</v>
+      </c>
       <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>0.553292</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.514203</v>
+      </c>
       <c r="J13" t="n">
-        <v>0.242262</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
+        <v>0.202035</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.508571</v>
+      </c>
       <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
+        <v>0.523529</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.515942</v>
+      </c>
       <c r="N13" t="n">
         <v>0.2</v>
       </c>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_3.txt</t>
+          <t>_2_3_3_3_1_1790731906_18.txt</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1761,7 +1761,7 @@
         <v>0.1</v>
       </c>
       <c r="B14" t="n">
-        <v>0.187001</v>
+        <v>0.187279</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1778,25 +1778,25 @@
         <v>200000</v>
       </c>
       <c r="G14" t="n">
-        <v>0.606218</v>
+        <v>0.584615</v>
       </c>
       <c r="H14" t="n">
-        <v>0.550157</v>
+        <v>0.53605</v>
       </c>
       <c r="I14" t="n">
-        <v>0.576828</v>
+        <v>0.55928</v>
       </c>
       <c r="J14" t="n">
-        <v>0.185416</v>
+        <v>0.187293</v>
       </c>
       <c r="K14" t="n">
-        <v>0.618056</v>
+        <v>0.581081</v>
       </c>
       <c r="L14" t="n">
-        <v>0.523529</v>
+        <v>0.5058820000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0.566879</v>
+        <v>0.5408809999999999</v>
       </c>
       <c r="N14" t="n">
         <v>0.2</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_15.txt</t>
+          <t>_2_9_1_1790731855_14.txt</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1862,7 +1862,7 @@
         <v>0.1</v>
       </c>
       <c r="B15" t="n">
-        <v>0.175709</v>
+        <v>0.194369</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1879,25 +1879,25 @@
         <v>200000</v>
       </c>
       <c r="G15" t="n">
-        <v>0.60089</v>
+        <v>0.566517</v>
       </c>
       <c r="H15" t="n">
-        <v>0.634796</v>
+        <v>0.594044</v>
       </c>
       <c r="I15" t="n">
-        <v>0.617378</v>
+        <v>0.579954</v>
       </c>
       <c r="J15" t="n">
-        <v>0.175519</v>
+        <v>0.192252</v>
       </c>
       <c r="K15" t="n">
-        <v>0.602339</v>
+        <v>0.603261</v>
       </c>
       <c r="L15" t="n">
-        <v>0.605882</v>
+        <v>0.652941</v>
       </c>
       <c r="M15" t="n">
-        <v>0.604106</v>
+        <v>0.627119</v>
       </c>
       <c r="N15" t="n">
         <v>0.2</v>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_5.txt</t>
+          <t>_2_9_1_1790731855_2.txt</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -1963,42 +1963,42 @@
         <v>0.1</v>
       </c>
       <c r="B16" t="n">
-        <v>0.20055</v>
+        <v>0.18153</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1790731906</v>
+        <v>1790731855</v>
       </c>
       <c r="E16" t="n">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="F16" t="n">
         <v>200000</v>
       </c>
       <c r="G16" t="n">
-        <v>0.485215</v>
+        <v>0.606759</v>
       </c>
       <c r="H16" t="n">
-        <v>0.565831</v>
+        <v>0.619122</v>
       </c>
       <c r="I16" t="n">
-        <v>0.522431</v>
+        <v>0.612878</v>
       </c>
       <c r="J16" t="n">
-        <v>0.20174</v>
+        <v>0.181627</v>
       </c>
       <c r="K16" t="n">
-        <v>0.508571</v>
+        <v>0.620482</v>
       </c>
       <c r="L16" t="n">
-        <v>0.523529</v>
+        <v>0.605882</v>
       </c>
       <c r="M16" t="n">
-        <v>0.515942</v>
+        <v>0.6130949999999999</v>
       </c>
       <c r="N16" t="n">
         <v>0.2</v>
@@ -2034,23 +2034,23 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_0.txt</t>
+          <t>_2_9_1_1790731855_6.txt</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z16" t="n">
         <v>9</v>
       </c>
       <c r="AA16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2064,42 +2064,42 @@
         <v>0.1</v>
       </c>
       <c r="B17" t="n">
-        <v>0.212929</v>
+        <v>0.195504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1790731906</v>
+        <v>1790731855</v>
       </c>
       <c r="E17" t="n">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="F17" t="n">
         <v>200000</v>
       </c>
       <c r="G17" t="n">
-        <v>0.414763</v>
+        <v>0.547198</v>
       </c>
       <c r="H17" t="n">
-        <v>0.369906</v>
+        <v>0.581505</v>
       </c>
       <c r="I17" t="n">
-        <v>0.391052</v>
+        <v>0.5638300000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.216066</v>
+        <v>0.193585</v>
       </c>
       <c r="K17" t="n">
-        <v>0.435714</v>
+        <v>0.606557</v>
       </c>
       <c r="L17" t="n">
-        <v>0.358824</v>
+        <v>0.652941</v>
       </c>
       <c r="M17" t="n">
-        <v>0.393548</v>
+        <v>0.628895</v>
       </c>
       <c r="N17" t="n">
         <v>0.2</v>
@@ -2135,23 +2135,23 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_5.txt</t>
+          <t>_2_9_1_1790731855_19.txt</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z17" t="n">
         <v>9</v>
       </c>
       <c r="AA17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2165,7 +2165,7 @@
         <v>0.1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.239696</v>
+        <v>0.239726</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>0.245175</v>
+        <v>0.245134</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_16.txt</t>
+          <t>_2_3_3_3_1_1790731906_7.txt</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2258,35 +2258,43 @@
         <v>0.1</v>
       </c>
       <c r="B19" t="n">
-        <v>0.239745</v>
+        <v>0.178531</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1790731906</v>
+        <v>1790731855</v>
       </c>
       <c r="E19" t="n">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="F19" t="n">
         <v>200000</v>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>0.62543</v>
+      </c>
       <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>0.570533</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.5967209999999999</v>
+      </c>
       <c r="J19" t="n">
-        <v>0.245058</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
+        <v>0.177521</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.639456</v>
+      </c>
       <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
+        <v>0.552941</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.59306</v>
+      </c>
       <c r="N19" t="n">
         <v>0.2</v>
       </c>
@@ -2321,23 +2329,23 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_10.txt</t>
+          <t>_2_9_1_1790731855_8.txt</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z19" t="n">
         <v>9</v>
       </c>
       <c r="AA19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2351,35 +2359,43 @@
         <v>0.1</v>
       </c>
       <c r="B20" t="n">
-        <v>0.232498</v>
+        <v>0.186458</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1790731906</v>
+        <v>1790731855</v>
       </c>
       <c r="E20" t="n">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="F20" t="n">
         <v>200000</v>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0.586207</v>
+      </c>
       <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>0.559561</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.572574</v>
+      </c>
       <c r="J20" t="n">
-        <v>0.241625</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
+        <v>0.183805</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.594771</v>
+      </c>
       <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="inlineStr"/>
+        <v>0.535294</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.5634670000000001</v>
+      </c>
       <c r="N20" t="n">
         <v>0.2</v>
       </c>
@@ -2414,23 +2430,23 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_14.txt</t>
+          <t>_2_9_1_1790731855_16.txt</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z20" t="n">
         <v>9</v>
       </c>
       <c r="AA20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2444,42 +2460,42 @@
         <v>0.1</v>
       </c>
       <c r="B21" t="n">
-        <v>0.183285</v>
+        <v>0.207824</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1790731855</v>
+        <v>1790731906</v>
       </c>
       <c r="E21" t="n">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="F21" t="n">
         <v>200000</v>
       </c>
       <c r="G21" t="n">
-        <v>0.612737</v>
+        <v>0.439577</v>
       </c>
       <c r="H21" t="n">
-        <v>0.557994</v>
+        <v>0.456113</v>
       </c>
       <c r="I21" t="n">
-        <v>0.584085</v>
+        <v>0.447692</v>
       </c>
       <c r="J21" t="n">
-        <v>0.181766</v>
+        <v>0.207962</v>
       </c>
       <c r="K21" t="n">
-        <v>0.601351</v>
+        <v>0.461538</v>
       </c>
       <c r="L21" t="n">
-        <v>0.523529</v>
+        <v>0.423529</v>
       </c>
       <c r="M21" t="n">
-        <v>0.559748</v>
+        <v>0.441718</v>
       </c>
       <c r="N21" t="n">
         <v>0.2</v>
@@ -2515,23 +2531,23 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_10.txt</t>
+          <t>_2_3_3_3_1_1790731906_17.txt</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z21" t="n">
         <v>9</v>
       </c>
       <c r="AA21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2545,7 +2561,7 @@
         <v>0.1</v>
       </c>
       <c r="B22" t="n">
-        <v>0.239681</v>
+        <v>0.235884</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2567,7 +2583,7 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>0.244739</v>
+        <v>0.240593</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
@@ -2608,7 +2624,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_19.txt</t>
+          <t>_2_3_3_3_1_1790731906_9.txt</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2731,7 +2747,7 @@
         <v>0.1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.18153</v>
+        <v>0.187204</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2748,25 +2764,25 @@
         <v>200000</v>
       </c>
       <c r="G24" t="n">
-        <v>0.606759</v>
+        <v>0.605422</v>
       </c>
       <c r="H24" t="n">
-        <v>0.619122</v>
+        <v>0.630094</v>
       </c>
       <c r="I24" t="n">
-        <v>0.612878</v>
+        <v>0.6175119999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>0.181627</v>
+        <v>0.185579</v>
       </c>
       <c r="K24" t="n">
-        <v>0.620482</v>
+        <v>0.6172840000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>0.605882</v>
+        <v>0.588235</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6130949999999999</v>
+        <v>0.60241</v>
       </c>
       <c r="N24" t="n">
         <v>0.2</v>
@@ -2802,7 +2818,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_6.txt</t>
+          <t>_2_9_1_1790731855_7.txt</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2832,35 +2848,43 @@
         <v>0.1</v>
       </c>
       <c r="B25" t="n">
-        <v>0.239726</v>
+        <v>0.184337</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1790731906</v>
+        <v>1790731855</v>
       </c>
       <c r="E25" t="n">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="F25" t="n">
         <v>200000</v>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>0.5855860000000001</v>
+      </c>
       <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>0.611285</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.59816</v>
+      </c>
       <c r="J25" t="n">
-        <v>0.245134</v>
-      </c>
-      <c r="K25" t="inlineStr"/>
+        <v>0.181985</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.647436</v>
+      </c>
       <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr"/>
+        <v>0.594118</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.619632</v>
+      </c>
       <c r="N25" t="n">
         <v>0.2</v>
       </c>
@@ -2895,23 +2919,23 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_7.txt</t>
+          <t>_2_9_1_1790731855_1.txt</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z25" t="n">
         <v>9</v>
       </c>
       <c r="AA25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -2925,42 +2949,42 @@
         <v>0.1</v>
       </c>
       <c r="B26" t="n">
-        <v>0.184698</v>
+        <v>0.188574</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1790731855</v>
+        <v>1790731906</v>
       </c>
       <c r="E26" t="n">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="F26" t="n">
         <v>200000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.587912</v>
+        <v>0.54567</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6708460000000001</v>
+        <v>0.7210029999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>0.626647</v>
+        <v>0.621202</v>
       </c>
       <c r="J26" t="n">
-        <v>0.182747</v>
+        <v>0.186506</v>
       </c>
       <c r="K26" t="n">
-        <v>0.594444</v>
+        <v>0.572139</v>
       </c>
       <c r="L26" t="n">
-        <v>0.629412</v>
+        <v>0.676471</v>
       </c>
       <c r="M26" t="n">
-        <v>0.611429</v>
+        <v>0.619946</v>
       </c>
       <c r="N26" t="n">
         <v>0.2</v>
@@ -2996,23 +3020,23 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_4.txt</t>
+          <t>_2_3_3_3_1_1790731906_15.txt</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z26" t="n">
         <v>9</v>
       </c>
       <c r="AA26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3026,7 +3050,7 @@
         <v>0.1</v>
       </c>
       <c r="B27" t="n">
-        <v>0.194369</v>
+        <v>0.188023</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3043,25 +3067,25 @@
         <v>200000</v>
       </c>
       <c r="G27" t="n">
-        <v>0.566517</v>
+        <v>0.60134</v>
       </c>
       <c r="H27" t="n">
-        <v>0.594044</v>
+        <v>0.562696</v>
       </c>
       <c r="I27" t="n">
-        <v>0.579954</v>
+        <v>0.581376</v>
       </c>
       <c r="J27" t="n">
-        <v>0.192252</v>
+        <v>0.186329</v>
       </c>
       <c r="K27" t="n">
-        <v>0.603261</v>
+        <v>0.597222</v>
       </c>
       <c r="L27" t="n">
-        <v>0.652941</v>
+        <v>0.5058820000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>0.627119</v>
+        <v>0.547771</v>
       </c>
       <c r="N27" t="n">
         <v>0.2</v>
@@ -3097,7 +3121,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_2.txt</t>
+          <t>_2_9_1_1790731855_3.txt</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3127,7 +3151,7 @@
         <v>0.1</v>
       </c>
       <c r="B28" t="n">
-        <v>0.239731</v>
+        <v>0.239745</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3149,7 +3173,7 @@
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>0.244998</v>
+        <v>0.245058</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
@@ -3190,7 +3214,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_2.txt</t>
+          <t>_2_3_3_3_1_1790731906_10.txt</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3220,42 +3244,42 @@
         <v>0.1</v>
       </c>
       <c r="B29" t="n">
-        <v>0.207824</v>
+        <v>0.187001</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1790731906</v>
+        <v>1790731855</v>
       </c>
       <c r="E29" t="n">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="F29" t="n">
         <v>200000</v>
       </c>
       <c r="G29" t="n">
-        <v>0.439577</v>
+        <v>0.606218</v>
       </c>
       <c r="H29" t="n">
-        <v>0.456113</v>
+        <v>0.550157</v>
       </c>
       <c r="I29" t="n">
-        <v>0.447692</v>
+        <v>0.576828</v>
       </c>
       <c r="J29" t="n">
-        <v>0.207962</v>
+        <v>0.185416</v>
       </c>
       <c r="K29" t="n">
-        <v>0.461538</v>
+        <v>0.618056</v>
       </c>
       <c r="L29" t="n">
-        <v>0.423529</v>
+        <v>0.523529</v>
       </c>
       <c r="M29" t="n">
-        <v>0.441718</v>
+        <v>0.566879</v>
       </c>
       <c r="N29" t="n">
         <v>0.2</v>
@@ -3291,23 +3315,23 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_17.txt</t>
+          <t>_2_9_1_1790731855_15.txt</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z29" t="n">
         <v>9</v>
       </c>
       <c r="AA29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3321,7 +3345,7 @@
         <v>0.1</v>
       </c>
       <c r="B30" t="n">
-        <v>0.179939</v>
+        <v>0.215095</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3338,25 +3362,25 @@
         <v>200000</v>
       </c>
       <c r="G30" t="n">
-        <v>0.573497</v>
+        <v>0.423598</v>
       </c>
       <c r="H30" t="n">
-        <v>0.80721</v>
+        <v>0.34326</v>
       </c>
       <c r="I30" t="n">
-        <v>0.670573</v>
+        <v>0.379221</v>
       </c>
       <c r="J30" t="n">
-        <v>0.178568</v>
+        <v>0.217713</v>
       </c>
       <c r="K30" t="n">
-        <v>0.61086</v>
+        <v>0.424</v>
       </c>
       <c r="L30" t="n">
-        <v>0.794118</v>
+        <v>0.311765</v>
       </c>
       <c r="M30" t="n">
-        <v>0.690537</v>
+        <v>0.359322</v>
       </c>
       <c r="N30" t="n">
         <v>0.2</v>
@@ -3392,7 +3416,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_11.txt</t>
+          <t>_2_3_3_3_1_1790731906_4.txt</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3422,7 +3446,7 @@
         <v>0.1</v>
       </c>
       <c r="B31" t="n">
-        <v>0.188574</v>
+        <v>0.20055</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3439,25 +3463,25 @@
         <v>200000</v>
       </c>
       <c r="G31" t="n">
-        <v>0.54567</v>
+        <v>0.485215</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7210029999999999</v>
+        <v>0.565831</v>
       </c>
       <c r="I31" t="n">
-        <v>0.621202</v>
+        <v>0.522431</v>
       </c>
       <c r="J31" t="n">
-        <v>0.186506</v>
+        <v>0.20174</v>
       </c>
       <c r="K31" t="n">
-        <v>0.572139</v>
+        <v>0.508571</v>
       </c>
       <c r="L31" t="n">
-        <v>0.676471</v>
+        <v>0.523529</v>
       </c>
       <c r="M31" t="n">
-        <v>0.619946</v>
+        <v>0.515942</v>
       </c>
       <c r="N31" t="n">
         <v>0.2</v>
@@ -3493,7 +3517,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_15.txt</t>
+          <t>_2_3_3_3_1_1790731906_0.txt</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3523,43 +3547,35 @@
         <v>0.1</v>
       </c>
       <c r="B32" t="n">
-        <v>0.18741</v>
+        <v>0.236222</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1790731855</v>
+        <v>1790731906</v>
       </c>
       <c r="E32" t="n">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="F32" t="n">
         <v>200000</v>
       </c>
-      <c r="G32" t="n">
-        <v>0.565035</v>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>0.633229</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.597191</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>0.185941</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.577778</v>
-      </c>
+        <v>0.242453</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
-        <v>0.611765</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.594286</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
         <v>0.2</v>
       </c>
@@ -3594,23 +3610,23 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_17.txt</t>
+          <t>_2_3_3_3_1_1790731906_13.txt</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z32" t="n">
         <v>9</v>
       </c>
       <c r="AA32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -3624,42 +3640,42 @@
         <v>0.1</v>
       </c>
       <c r="B33" t="n">
-        <v>0.184337</v>
+        <v>0.179939</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1790731855</v>
+        <v>1790731906</v>
       </c>
       <c r="E33" t="n">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="F33" t="n">
         <v>200000</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5855860000000001</v>
+        <v>0.573497</v>
       </c>
       <c r="H33" t="n">
-        <v>0.611285</v>
+        <v>0.80721</v>
       </c>
       <c r="I33" t="n">
-        <v>0.59816</v>
+        <v>0.670573</v>
       </c>
       <c r="J33" t="n">
-        <v>0.181985</v>
+        <v>0.178568</v>
       </c>
       <c r="K33" t="n">
-        <v>0.647436</v>
+        <v>0.61086</v>
       </c>
       <c r="L33" t="n">
-        <v>0.594118</v>
+        <v>0.794118</v>
       </c>
       <c r="M33" t="n">
-        <v>0.619632</v>
+        <v>0.690537</v>
       </c>
       <c r="N33" t="n">
         <v>0.2</v>
@@ -3695,23 +3711,23 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_1.txt</t>
+          <t>_2_3_3_3_1_1790731906_11.txt</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z33" t="n">
         <v>9</v>
       </c>
       <c r="AA33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -3725,43 +3741,35 @@
         <v>0.1</v>
       </c>
       <c r="B34" t="n">
-        <v>0.188023</v>
+        <v>0.232982</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1790731855</v>
+        <v>1790731906</v>
       </c>
       <c r="E34" t="n">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="F34" t="n">
         <v>200000</v>
       </c>
-      <c r="G34" t="n">
-        <v>0.60134</v>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>0.562696</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.581376</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>0.186329</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.597222</v>
-      </c>
+        <v>0.239653</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>0.5058820000000001</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.547771</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
         <v>0.2</v>
       </c>
@@ -3796,23 +3804,23 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_3.txt</t>
+          <t>_2_3_3_3_1_1790731906_1.txt</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z34" t="n">
         <v>9</v>
       </c>
       <c r="AA34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -3826,7 +3834,7 @@
         <v>0.1</v>
       </c>
       <c r="B35" t="n">
-        <v>0.200892</v>
+        <v>0.234166</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -3842,27 +3850,19 @@
       <c r="F35" t="n">
         <v>200000</v>
       </c>
-      <c r="G35" t="n">
-        <v>0.480272</v>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>0.553292</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.514203</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>0.202035</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.508571</v>
-      </c>
+        <v>0.241451</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>0.523529</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.515942</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
         <v>0.2</v>
       </c>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_18.txt</t>
+          <t>_2_3_3_3_1_1790731906_12.txt</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -3927,7 +3927,7 @@
         <v>0.1</v>
       </c>
       <c r="B36" t="n">
-        <v>0.180299</v>
+        <v>0.187187</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -3944,25 +3944,25 @@
         <v>200000</v>
       </c>
       <c r="G36" t="n">
-        <v>0.611501</v>
+        <v>0.602671</v>
       </c>
       <c r="H36" t="n">
-        <v>0.683386</v>
+        <v>0.565831</v>
       </c>
       <c r="I36" t="n">
-        <v>0.645448</v>
+        <v>0.58367</v>
       </c>
       <c r="J36" t="n">
-        <v>0.178741</v>
+        <v>0.184759</v>
       </c>
       <c r="K36" t="n">
-        <v>0.623711</v>
+        <v>0.601307</v>
       </c>
       <c r="L36" t="n">
-        <v>0.711765</v>
+        <v>0.541176</v>
       </c>
       <c r="M36" t="n">
-        <v>0.664835</v>
+        <v>0.569659</v>
       </c>
       <c r="N36" t="n">
         <v>0.2</v>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_13.txt</t>
+          <t>_2_9_1_1790731855_11.txt</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4028,42 +4028,42 @@
         <v>0.1</v>
       </c>
       <c r="B37" t="n">
-        <v>0.179406</v>
+        <v>0.212929</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1790731855</v>
+        <v>1790731906</v>
       </c>
       <c r="E37" t="n">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="F37" t="n">
         <v>200000</v>
       </c>
       <c r="G37" t="n">
-        <v>0.576816</v>
+        <v>0.414763</v>
       </c>
       <c r="H37" t="n">
-        <v>0.647335</v>
+        <v>0.369906</v>
       </c>
       <c r="I37" t="n">
-        <v>0.610044</v>
+        <v>0.391052</v>
       </c>
       <c r="J37" t="n">
-        <v>0.177572</v>
+        <v>0.216066</v>
       </c>
       <c r="K37" t="n">
-        <v>0.576923</v>
+        <v>0.435714</v>
       </c>
       <c r="L37" t="n">
-        <v>0.6176469999999999</v>
+        <v>0.358824</v>
       </c>
       <c r="M37" t="n">
-        <v>0.596591</v>
+        <v>0.393548</v>
       </c>
       <c r="N37" t="n">
         <v>0.2</v>
@@ -4099,23 +4099,23 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_9.txt</t>
+          <t>_2_3_3_3_1_1790731906_5.txt</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z37" t="n">
         <v>9</v>
       </c>
       <c r="AA37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4129,7 +4129,7 @@
         <v>0.1</v>
       </c>
       <c r="B38" t="n">
-        <v>0.187187</v>
+        <v>0.183285</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4146,25 +4146,25 @@
         <v>200000</v>
       </c>
       <c r="G38" t="n">
-        <v>0.602671</v>
+        <v>0.612737</v>
       </c>
       <c r="H38" t="n">
-        <v>0.565831</v>
+        <v>0.557994</v>
       </c>
       <c r="I38" t="n">
-        <v>0.58367</v>
+        <v>0.584085</v>
       </c>
       <c r="J38" t="n">
-        <v>0.184759</v>
+        <v>0.181766</v>
       </c>
       <c r="K38" t="n">
-        <v>0.601307</v>
+        <v>0.601351</v>
       </c>
       <c r="L38" t="n">
-        <v>0.541176</v>
+        <v>0.523529</v>
       </c>
       <c r="M38" t="n">
-        <v>0.569659</v>
+        <v>0.559748</v>
       </c>
       <c r="N38" t="n">
         <v>0.2</v>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731855_11.txt</t>
+          <t>_2_9_1_1790731855_10.txt</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4230,7 +4230,7 @@
         <v>0.1</v>
       </c>
       <c r="B39" t="n">
-        <v>0.233962</v>
+        <v>0.239696</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>0.240591</v>
+        <v>0.245175</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_6.txt</t>
+          <t>_2_3_3_3_1_1790731906_16.txt</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4323,7 +4323,7 @@
         <v>0.1</v>
       </c>
       <c r="B40" t="n">
-        <v>0.215095</v>
+        <v>0.239681</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4339,27 +4339,19 @@
       <c r="F40" t="n">
         <v>200000</v>
       </c>
-      <c r="G40" t="n">
-        <v>0.423598</v>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>0.34326</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.379221</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>0.217713</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.424</v>
-      </c>
+        <v>0.244739</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>0.311765</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.359322</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
         <v>0.2</v>
       </c>
@@ -4394,7 +4386,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_4.txt</t>
+          <t>_2_3_3_3_1_1790731906_19.txt</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4424,35 +4416,43 @@
         <v>0.1</v>
       </c>
       <c r="B41" t="n">
-        <v>0.234166</v>
+        <v>0.179942</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1790731906</v>
+        <v>1790731855</v>
       </c>
       <c r="E41" t="n">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="F41" t="n">
         <v>200000</v>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>0.622614</v>
+      </c>
       <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
+        <v>0.664577</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.642911</v>
+      </c>
       <c r="J41" t="n">
-        <v>0.241451</v>
-      </c>
-      <c r="K41" t="inlineStr"/>
+        <v>0.181995</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.630682</v>
+      </c>
       <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="inlineStr"/>
+        <v>0.652941</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.641618</v>
+      </c>
       <c r="N41" t="n">
         <v>0.2</v>
       </c>
@@ -4487,23 +4487,23 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731906_12.txt</t>
+          <t>_2_9_1_1790731855_18.txt</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z41" t="n">
         <v>9</v>
       </c>
       <c r="AA41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -4606,7 +4606,7 @@
         <v>0.59388395</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03570331577035062</v>
+        <v>0.03570331577035063</v>
       </c>
       <c r="D3" t="n">
         <v>0.664835</v>
